--- a/Hoadon/HDVao/11/3502386218_HDDienTuKhongMa.xlsx
+++ b/Hoadon/HDVao/11/3502386218_HDDienTuKhongMa.xlsx
@@ -1865,30 +1865,34 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>K25TDA</t>
+          <t>K25TCA</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>1514961</t>
+          <t>42322912</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>02/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>0300951119-010</t>
+          <t>0108269207</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H27" s="6"/>
+          <t>CÔNG TY CỔ PHẦN BE GROUP</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>Tầng 16, Tòa nhà Sai Gon Tower, 29 Lê Duẩn, Phường Sài Gòn, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
           <t>3502386218</t>
@@ -1896,19 +1900,19 @@
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>Công ty TNHH The FORUM EDUCATION</t>
+          <t>Công ty TNHH The Forum Education Vietnam</t>
         </is>
       </c>
       <c r="K27" s="13" t="n">
-        <v>3819816.0</v>
+        <v>139073.0</v>
       </c>
       <c r="L27" s="13" t="n">
-        <v>305585.0</v>
+        <v>8927.0</v>
       </c>
       <c r="M27" s="13"/>
       <c r="N27" s="13"/>
       <c r="O27" s="13" t="n">
-        <v>4125401.0</v>
+        <v>148000.0</v>
       </c>
       <c r="P27" s="7" t="inlineStr">
         <is>
@@ -1942,30 +1946,34 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>K25TDA</t>
+          <t>K25TCA</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>1514967</t>
+          <t>42538179</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>02/11/2025</t>
+          <t>18/11/2025</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>0300951119-010</t>
+          <t>0108269207</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H28" s="6"/>
+          <t>CÔNG TY CỔ PHẦN BE GROUP</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>Tầng 16, Tòa nhà Sai Gon Tower, 29 Lê Duẩn, Phường Sài Gòn, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
           <t>3502386218</t>
@@ -1973,19 +1981,19 @@
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+          <t>Công ty TNHH The Forum Education Vietnam</t>
         </is>
       </c>
       <c r="K28" s="13" t="n">
-        <v>1090740.0</v>
+        <v>44164.0</v>
       </c>
       <c r="L28" s="13" t="n">
-        <v>87259.0</v>
+        <v>2836.0</v>
       </c>
       <c r="M28" s="13"/>
       <c r="N28" s="13"/>
       <c r="O28" s="13" t="n">
-        <v>1177999.0</v>
+        <v>47000.0</v>
       </c>
       <c r="P28" s="7" t="inlineStr">
         <is>
@@ -2019,30 +2027,34 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>K25TDA</t>
+          <t>K25TCA</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>1515080</t>
+          <t>42744822</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>02/11/2025</t>
+          <t>19/11/2025</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>0300951119-010</t>
+          <t>0108269207</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H29" s="6"/>
+          <t>CÔNG TY CỔ PHẦN BE GROUP</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>Tầng 16, Tòa nhà Sai Gon Tower, 29 Lê Duẩn, Phường Sài Gòn, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
           <t>3502386218</t>
@@ -2050,19 +2062,19 @@
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIỆT NAM</t>
+          <t>Công ty TNHH The Forum Education Vietnam</t>
         </is>
       </c>
       <c r="K29" s="13" t="n">
-        <v>2642262.0</v>
+        <v>53325.0</v>
       </c>
       <c r="L29" s="13" t="n">
-        <v>211381.0</v>
+        <v>3675.0</v>
       </c>
       <c r="M29" s="13"/>
       <c r="N29" s="13"/>
       <c r="O29" s="13" t="n">
-        <v>2853643.0</v>
+        <v>57000.0</v>
       </c>
       <c r="P29" s="7" t="inlineStr">
         <is>
@@ -2101,7 +2113,7 @@
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>1535987</t>
+          <t>1514961</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
@@ -2127,19 +2139,19 @@
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>Công Ty TNHH The Forum Education Vietnam</t>
+          <t>Công ty TNHH The FORUM EDUCATION</t>
         </is>
       </c>
       <c r="K30" s="13" t="n">
-        <v>2867088.0</v>
+        <v>3819816.0</v>
       </c>
       <c r="L30" s="13" t="n">
-        <v>229367.0</v>
+        <v>305585.0</v>
       </c>
       <c r="M30" s="13"/>
       <c r="N30" s="13"/>
       <c r="O30" s="13" t="n">
-        <v>3096455.0</v>
+        <v>4125401.0</v>
       </c>
       <c r="P30" s="7" t="inlineStr">
         <is>
@@ -2178,7 +2190,7 @@
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>1535989</t>
+          <t>1514967</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
@@ -2204,19 +2216,19 @@
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>Công Ty TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
         </is>
       </c>
       <c r="K31" s="13" t="n">
-        <v>3739680.0</v>
+        <v>1090740.0</v>
       </c>
       <c r="L31" s="13" t="n">
-        <v>299174.0</v>
+        <v>87259.0</v>
       </c>
       <c r="M31" s="13"/>
       <c r="N31" s="13"/>
       <c r="O31" s="13" t="n">
-        <v>4038854.0</v>
+        <v>1177999.0</v>
       </c>
       <c r="P31" s="7" t="inlineStr">
         <is>
@@ -2255,7 +2267,7 @@
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>1535991</t>
+          <t>1515080</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
@@ -2281,19 +2293,19 @@
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>Công Ty TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIỆT NAM</t>
         </is>
       </c>
       <c r="K32" s="13" t="n">
-        <v>2668974.0</v>
+        <v>2642262.0</v>
       </c>
       <c r="L32" s="13" t="n">
-        <v>213518.0</v>
+        <v>211381.0</v>
       </c>
       <c r="M32" s="13"/>
       <c r="N32" s="13"/>
       <c r="O32" s="13" t="n">
-        <v>2882492.0</v>
+        <v>2853643.0</v>
       </c>
       <c r="P32" s="7" t="inlineStr">
         <is>
@@ -2332,7 +2344,7 @@
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>1537215</t>
+          <t>1535987</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
@@ -2358,19 +2370,19 @@
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>Công ty TNHH The Forum EDUCATION VIETNAM</t>
+          <t>Công Ty TNHH The Forum Education Vietnam</t>
         </is>
       </c>
       <c r="K33" s="13" t="n">
-        <v>149142.0</v>
+        <v>2867088.0</v>
       </c>
       <c r="L33" s="13" t="n">
-        <v>11931.0</v>
+        <v>229367.0</v>
       </c>
       <c r="M33" s="13"/>
       <c r="N33" s="13"/>
       <c r="O33" s="13" t="n">
-        <v>161073.0</v>
+        <v>3096455.0</v>
       </c>
       <c r="P33" s="7" t="inlineStr">
         <is>
@@ -2409,12 +2421,12 @@
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>1586533</t>
+          <t>1535989</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>03/11/2025</t>
+          <t>02/11/2025</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
@@ -2435,19 +2447,19 @@
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>Công ty TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>Công Ty TNHH THE FORUM EDUCATION VIETNAM</t>
         </is>
       </c>
       <c r="K34" s="13" t="n">
-        <v>3639510.0</v>
+        <v>3739680.0</v>
       </c>
       <c r="L34" s="13" t="n">
-        <v>291161.0</v>
+        <v>299174.0</v>
       </c>
       <c r="M34" s="13"/>
       <c r="N34" s="13"/>
       <c r="O34" s="13" t="n">
-        <v>3930671.0</v>
+        <v>4038854.0</v>
       </c>
       <c r="P34" s="7" t="inlineStr">
         <is>
@@ -2481,12 +2493,12 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>K25THE</t>
+          <t>K25TDA</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>25387</t>
+          <t>1535991</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
@@ -2496,12 +2508,12 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>0300954529</t>
+          <t>0300951119-010</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>CHI NHÁNH TẬP ĐOÀN BƯU CHÍNH VIỄN THÔNG VIỆT NAM (LOẠI HÌNH DOANH NGHIỆP: CÔNG TY TNHH) - VIỄN THÔNG THÀNH PHỐ HỒ CHÍ MINH</t>
+          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
         </is>
       </c>
       <c r="H35" s="6"/>
@@ -2512,19 +2524,19 @@
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>Công Ty TNHH THE FORUM EDUCATION</t>
+          <t>Công Ty TNHH THE FORUM EDUCATION VIETNAM</t>
         </is>
       </c>
       <c r="K35" s="13" t="n">
-        <v>163454.0</v>
+        <v>2668974.0</v>
       </c>
       <c r="L35" s="13" t="n">
-        <v>16345.0</v>
+        <v>213518.0</v>
       </c>
       <c r="M35" s="13"/>
       <c r="N35" s="13"/>
       <c r="O35" s="13" t="n">
-        <v>179799.0</v>
+        <v>2882492.0</v>
       </c>
       <c r="P35" s="7" t="inlineStr">
         <is>
@@ -2558,12 +2570,12 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>K25THE</t>
+          <t>K25TDA</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>56102</t>
+          <t>1537215</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
@@ -2573,12 +2585,12 @@
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>0300954529</t>
+          <t>0300951119-010</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>CHI NHÁNH TẬP ĐOÀN BƯU CHÍNH VIỄN THÔNG VIỆT NAM (LOẠI HÌNH DOANH NGHIỆP: CÔNG TY TNHH) - VIỄN THÔNG THÀNH PHỐ HỒ CHÍ MINH</t>
+          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
         </is>
       </c>
       <c r="H36" s="6"/>
@@ -2589,36 +2601,267 @@
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIỆT NAM</t>
+          <t>Công ty TNHH The Forum EDUCATION VIETNAM</t>
         </is>
       </c>
       <c r="K36" s="13" t="n">
-        <v>2367937.0</v>
+        <v>149142.0</v>
       </c>
       <c r="L36" s="13" t="n">
-        <v>236794.0</v>
+        <v>11931.0</v>
       </c>
       <c r="M36" s="13"/>
       <c r="N36" s="13"/>
       <c r="O36" s="13" t="n">
+        <v>161073.0</v>
+      </c>
+      <c r="P36" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q36" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S36" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
+        <v>31.0</v>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>K25TDA</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>1586533</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>03/11/2025</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>0300951119-010</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H37" s="6"/>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>Công ty TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K37" s="13" t="n">
+        <v>3639510.0</v>
+      </c>
+      <c r="L37" s="13" t="n">
+        <v>291161.0</v>
+      </c>
+      <c r="M37" s="13"/>
+      <c r="N37" s="13"/>
+      <c r="O37" s="13" t="n">
+        <v>3930671.0</v>
+      </c>
+      <c r="P37" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q37" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S37" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>32.0</v>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>K25THE</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>25387</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>0300954529</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH TẬP ĐOÀN BƯU CHÍNH VIỄN THÔNG VIỆT NAM (LOẠI HÌNH DOANH NGHIỆP: CÔNG TY TNHH) - VIỄN THÔNG THÀNH PHỐ HỒ CHÍ MINH</t>
+        </is>
+      </c>
+      <c r="H38" s="6"/>
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH THE FORUM EDUCATION</t>
+        </is>
+      </c>
+      <c r="K38" s="13" t="n">
+        <v>163454.0</v>
+      </c>
+      <c r="L38" s="13" t="n">
+        <v>16345.0</v>
+      </c>
+      <c r="M38" s="13"/>
+      <c r="N38" s="13"/>
+      <c r="O38" s="13" t="n">
+        <v>179799.0</v>
+      </c>
+      <c r="P38" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q38" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S38" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>33.0</v>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>K25THE</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>56102</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>0300954529</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH TẬP ĐOÀN BƯU CHÍNH VIỄN THÔNG VIỆT NAM (LOẠI HÌNH DOANH NGHIỆP: CÔNG TY TNHH) - VIỄN THÔNG THÀNH PHỐ HỒ CHÍ MINH</t>
+        </is>
+      </c>
+      <c r="H39" s="6"/>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIỆT NAM</t>
+        </is>
+      </c>
+      <c r="K39" s="13" t="n">
+        <v>2367937.0</v>
+      </c>
+      <c r="L39" s="13" t="n">
+        <v>236794.0</v>
+      </c>
+      <c r="M39" s="13"/>
+      <c r="N39" s="13"/>
+      <c r="O39" s="13" t="n">
         <v>2604731.0</v>
       </c>
-      <c r="P36" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q36" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S36" s="6" t="inlineStr">
+      <c r="P39" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q39" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S39" s="6" t="inlineStr">
         <is>
           <t>Tổng cục thuế đã nhận không mã</t>
         </is>
